--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 01:40:50</t>
+          <t>2026-06-09 03:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -863,7 +863,7 @@
         <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I2" t="n">
         <v>3.15</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:49:16</t>
+          <t>2026-06-09 05:57:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 05:57:47</t>
+          <t>2026-06-09 08:06:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 08:06:14</t>
+          <t>2026-06-09 10:15:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -863,7 +863,7 @@
         <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
         <v>2.9</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:15:48</t>
+          <t>2026-06-09 12:24:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,34 +857,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -893,194 +893,194 @@
         <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:24:18</t>
+          <t>2026-06-09 14:37:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,13 +860,13 @@
         <v>2.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -875,16 +875,16 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -893,22 +893,22 @@
         <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1028,13 +1028,13 @@
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>1.69</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>1.95</v>
       </c>
       <c r="BN2" t="n">
         <v>7.8</v>
@@ -1046,13 +1046,13 @@
         <v>26</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>1.82</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>18.5</v>
+        <v>1.86</v>
       </c>
       <c r="BT2" t="n">
         <v>8</v>
@@ -1064,23 +1064,23 @@
         <v>29</v>
       </c>
       <c r="BW2" t="n">
-        <v>13</v>
+        <v>1.83</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>19</v>
+        <v>1.87</v>
       </c>
       <c r="BZ2" t="n">
         <v>30</v>
       </c>
       <c r="CA2" t="n">
-        <v>14</v>
+        <v>1.83</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:37:25</t>
+          <t>2026-06-09 16:45:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>2.84</v>
@@ -866,7 +866,7 @@
         <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -875,7 +875,7 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -884,7 +884,7 @@
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -893,25 +893,25 @@
         <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -932,7 +932,7 @@
         <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -941,7 +941,7 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AW2" t="n">
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>1.21</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>7.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
         <v>26</v>
@@ -1058,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>29</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 16:45:24</t>
+          <t>2026-06-09 20:43:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
         <v>2.84</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -896,7 +896,7 @@
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>1.35</v>
@@ -905,7 +905,7 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
         <v>1.54</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 20:43:34</t>
+          <t>2026-06-09 22:50:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
         <v>2.84</v>
@@ -866,7 +866,7 @@
         <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -875,16 +875,16 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -893,194 +893,194 @@
         <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
         <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.14</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.21</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.21</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.21</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.13</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.21</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.21</v>
+        <v>19.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.19</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.21</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.21</v>
+        <v>17.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.69</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.95</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.82</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.86</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.83</v>
+        <v>7.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.87</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.83</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-09 22:50:52</t>
+          <t>2026-06-10 00:58:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,10 +860,10 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
         <v>2.98</v>
@@ -872,10 +872,10 @@
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -884,19 +884,19 @@
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.65</v>
@@ -908,7 +908,7 @@
         <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,16 +917,16 @@
         <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -938,7 +938,7 @@
         <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
@@ -962,19 +962,19 @@
         <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -986,37 +986,37 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
         <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH2" t="n">
         <v>3.8</v>
@@ -1028,59 +1028,59 @@
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,210 +843,210 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>00:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>AV Alta FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sarasota Paradise</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
         <v>9</v>
       </c>
-      <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
         <v>22</v>
       </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>2.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1055,32 +1055,286 @@
         <v>7.6</v>
       </c>
       <c r="BT2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-10 05:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Helsingborgs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV2" t="n">
+      <c r="BU3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV3" t="n">
         <v>22</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="BW3" t="n">
         <v>6.8</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="BX3" t="n">
         <v>32</v>
       </c>
-      <c r="BY2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ2" t="n">
+      <c r="BY3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>24</v>
       </c>
-      <c r="CA2" t="n">
-        <v>7</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-10 03:05:10</t>
+      <c r="CA3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,55 +860,55 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
         <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
@@ -932,37 +932,37 @@
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
         <v>13.5</v>
@@ -977,16 +977,16 @@
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>1.05</v>
       </c>
       <c r="AX2" t="n">
         <v>12</v>
@@ -995,19 +995,19 @@
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>1.05</v>
       </c>
       <c r="BE2" t="n">
         <v>1.01</v>
@@ -1016,13 +1016,13 @@
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>1.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.76</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1043,7 +1043,7 @@
         <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.4</v>
@@ -1058,7 +1058,7 @@
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1138,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -1147,13 +1147,13 @@
         <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
         <v>2.26</v>
@@ -1162,25 +1162,25 @@
         <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB3" t="n">
         <v>15</v>
       </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>14</v>
-      </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1192,10 +1192,10 @@
         <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
@@ -1207,10 +1207,10 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
         <v>21</v>
@@ -1219,82 +1219,82 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN3" t="n">
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
         <v>20</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
         <v>6.4</v>
@@ -1324,17 +1324,17 @@
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA3" t="n">
         <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.65</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -884,10 +884,10 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
@@ -896,25 +896,25 @@
         <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
         <v>29</v>
@@ -923,19 +923,19 @@
         <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -965,13 +965,13 @@
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
@@ -989,7 +989,7 @@
         <v>1.05</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>8.6</v>
@@ -1001,10 +1001,10 @@
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>1.05</v>
@@ -1013,10 +1013,10 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.05</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="n">
         <v>4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
         <v>2.74</v>
@@ -1153,10 +1153,10 @@
         <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.51</v>
@@ -1195,7 +1195,7 @@
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
@@ -1222,25 +1222,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>14</v>
@@ -1252,25 +1252,25 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
@@ -1282,7 +1282,7 @@
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
         <v>20</v>
@@ -1312,7 +1312,7 @@
         <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1334,7 +1334,261 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ymir</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KA Asvellir</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,13 +860,13 @@
         <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -884,31 +884,31 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -965,112 +965,112 @@
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
         <v>2.74</v>
@@ -1129,7 +1129,7 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1147,16 +1147,16 @@
         <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.51</v>
@@ -1198,34 +1198,34 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
         <v>32</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
         <v>14</v>
@@ -1249,28 +1249,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>20</v>
@@ -1303,7 +1303,7 @@
         <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS3" t="n">
         <v>7.6</v>
@@ -1312,7 +1312,7 @@
         <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1389,28 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1530,55 +1530,55 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -866,7 +866,7 @@
         <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -884,7 +884,7 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
@@ -905,7 +905,7 @@
         <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>1.74</v>
@@ -935,7 +935,7 @@
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -950,127 +950,127 @@
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>2.74</v>
@@ -1129,7 +1129,7 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1198,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
         <v>42</v>
@@ -1219,7 +1219,7 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -1234,7 +1234,7 @@
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
@@ -1249,22 +1249,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1282,7 +1282,7 @@
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
         <v>20</v>
@@ -1312,7 +1312,7 @@
         <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 11:40:19</t>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,16 +998,16 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
         <v>2.96</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1147,16 +1147,16 @@
         <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.51</v>
@@ -1189,7 +1189,7 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
@@ -1219,7 +1219,7 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
         <v>14</v>
@@ -1252,19 +1252,19 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,22 +860,22 @@
         <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -887,97 +887,97 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
         <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AD2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
         <v>16</v>
       </c>
-      <c r="AE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>1.13</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7</v>
@@ -986,7 +986,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,79 +998,79 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>1.13</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1135,7 +1135,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1144,28 +1144,28 @@
         <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
         <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>15.5</v>
@@ -1183,55 +1183,55 @@
         <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
         <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
@@ -1240,37 +1240,37 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH3" t="n">
         <v>3.85</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
         <v>6</v>
@@ -1297,13 +1297,13 @@
         <v>5</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BR3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS3" t="n">
         <v>7.6</v>
@@ -1318,23 +1318,23 @@
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>23</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
         <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>1.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -860,7 +860,7 @@
         <v>2.18</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -869,10 +869,10 @@
         <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -890,19 +890,19 @@
         <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -911,61 +911,61 @@
         <v>1.72</v>
       </c>
       <c r="X2" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP2" t="n">
         <v>16</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
@@ -974,7 +974,7 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
         <v>9.6</v>
@@ -986,31 +986,31 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1034,10 +1034,10 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
@@ -1046,31 +1046,31 @@
         <v>16.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -1144,22 +1144,22 @@
         <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
@@ -1168,55 +1168,55 @@
         <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
         <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
         <v>34</v>
       </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
         <v>14.5</v>
@@ -1240,7 +1240,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>16</v>
@@ -1252,19 +1252,19 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1300,7 +1300,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>30</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I4" t="n">
         <v>3.65</v>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.06</v>
@@ -1413,118 +1413,118 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
         <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -887,13 +887,13 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
         <v>2.86</v>
@@ -908,85 +908,85 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16</v>
       </c>
       <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="n">
         <v>40</v>
       </c>
-      <c r="AF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AM2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -995,22 +995,22 @@
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1022,25 +1022,25 @@
         <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>70</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
         <v>16.5</v>
@@ -1049,7 +1049,7 @@
         <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
         <v>7.6</v>
@@ -1058,19 +1058,19 @@
         <v>7</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>26</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
         <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
         <v>2.88</v>
@@ -1132,10 +1132,10 @@
         <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1144,19 +1144,19 @@
         <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
         <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
         <v>1.53</v>
@@ -1198,7 +1198,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
@@ -1252,19 +1252,19 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1276,7 +1276,7 @@
         <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.72</v>
       </c>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I4" t="n">
         <v>3.65</v>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38</v>
+        <v>1.13</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN2" t="n">
         <v>3.45</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15</v>
-      </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>3.05</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
         <v>9.4</v>
       </c>
-      <c r="BK2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM2" t="n">
-        <v>70</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>1.78</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>1.56</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -1129,13 +1129,13 @@
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1147,25 +1147,25 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
@@ -1174,13 +1174,13 @@
         <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1189,7 +1189,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1198,7 +1198,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
@@ -1210,31 +1210,31 @@
         <v>100</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
@@ -1243,98 +1243,98 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
         <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>7</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BN3" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1473,52 +1473,52 @@
         <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BF4" t="n">
         <v>1.55</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AV Alta FC</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sarasota Paradise</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>1.13</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS2" t="n">
         <v>29</v>
       </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
         <v>10.5</v>
       </c>
-      <c r="K2" t="n">
-        <v>13</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="AW2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA2" t="n">
         <v>8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>960</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,180 +1097,180 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>2.24</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>1.69</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>17</v>
+        <v>1.21</v>
       </c>
       <c r="AS3" t="n">
-        <v>29</v>
+        <v>1.23</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>1.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>1.23</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>1.21</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>1.21</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>1.23</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>1.21</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>1.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>1.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1282,19 +1282,19 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,289 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Icelandic 3 Deild</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ymir</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>KA Asvellir</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X4" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -863,7 +863,7 @@
         <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
         <v>2.92</v>
@@ -872,7 +872,7 @@
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -881,25 +881,25 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
         <v>2.44</v>
@@ -914,115 +914,115 @@
         <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
         <v>100</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT2" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
         <v>30</v>
       </c>
       <c r="BB2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>18</v>
       </c>
-      <c r="BC2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
@@ -1031,7 +1031,7 @@
         <v>5.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM2" t="n">
         <v>11</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY2" t="n">
         <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
         <v>8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.17</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.69</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.73</v>
       </c>
       <c r="X3" t="n">
         <v>950</v>
@@ -1180,10 +1180,10 @@
         <v>950</v>
       </c>
       <c r="AC3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD3" t="n">
         <v>500</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1192,10 +1192,10 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1210,121 +1210,121 @@
         <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.23</v>
+        <v>3.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.23</v>
+        <v>3.85</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.21</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.23</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.21</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.23</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.21</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.22</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.86</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.92</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -890,76 +890,76 @@
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
         <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -968,73 +968,73 @@
         <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="n">
         <v>30</v>
       </c>
-      <c r="BB2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>29</v>
-      </c>
       <c r="BE2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>90</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>5.8</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>30</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -1117,10 +1117,10 @@
         <v>2.46</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q3" t="n">
         <v>1.27</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="U3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
         <v>950</v>
@@ -1192,10 +1192,10 @@
         <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1219,16 +1219,16 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.2</v>
@@ -1240,43 +1240,43 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>10</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD3" t="n">
         <v>6</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN3" t="n">
         <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,7 +1318,7 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Nigerian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Barau FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
         <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>4.7</v>
       </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.25</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.53</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>14</v>
       </c>
-      <c r="Z2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Nigerian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KA Asvellir</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.14</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.27</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="AN3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>310</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV3" t="n">
         <v>55</v>
       </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW3" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,515 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Helsingborgs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ymir</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KA Asvellir</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X5" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH2" t="n">
         <v>2.7</v>
       </c>
-      <c r="H2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BI2" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
         <v>14</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
         <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
         <v>48</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>75</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P3" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>8</v>
       </c>
       <c r="AC3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
         <v>15</v>
       </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL3" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>60</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>55</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
         <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
@@ -1425,7 +1425,7 @@
         <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
         <v>44</v>
@@ -1443,31 +1443,31 @@
         <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>23</v>
@@ -1479,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
         <v>38</v>
@@ -1497,19 +1497,19 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
         <v>32</v>
       </c>
       <c r="BB4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1521,28 +1521,28 @@
         <v>60</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
         <v>19.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>100</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>75</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
@@ -1554,10 +1554,10 @@
         <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
         <v>10</v>
@@ -1566,29 +1566,29 @@
         <v>6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
         <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -1646,7 +1646,7 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P5" t="n">
         <v>4.1</v>
@@ -1655,22 +1655,22 @@
         <v>1.27</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1688,22 +1688,22 @@
         <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AD5" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH5" t="n">
         <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1712,7 +1712,7 @@
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,25 +1721,25 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
         <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
@@ -1748,10 +1748,10 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
         <v>6.6</v>
@@ -1760,79 +1760,79 @@
         <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BN5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
         <v>5.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.17</v>
       </c>
-      <c r="S2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.69</v>
-      </c>
       <c r="X2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>1.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AV2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>14</v>
       </c>
-      <c r="AW2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>1.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.76</v>
+        <v>40</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>850</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>850</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY3" t="n">
         <v>30</v>
       </c>
-      <c r="AA3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AZ3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.9</v>
       </c>
-      <c r="AV3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1365,178 +1365,178 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="I4" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
         <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
         <v>29</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
         <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL4" t="n">
         <v>38</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD4" t="n">
         <v>32</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>60</v>
       </c>
       <c r="BF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG4" t="n">
         <v>19</v>
       </c>
-      <c r="BG4" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="n">
         <v>100</v>
@@ -1545,50 +1545,50 @@
         <v>75</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BX4" t="n">
         <v>32</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="CA4" t="n">
         <v>18.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
         <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1649,16 +1649,16 @@
         <v>1.08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T5" t="n">
         <v>1.3</v>
@@ -1670,7 +1670,7 @@
         <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1682,16 +1682,16 @@
         <v>500</v>
       </c>
       <c r="AA5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB5" t="n">
         <v>500</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>950</v>
       </c>
       <c r="AC5" t="n">
         <v>26</v>
       </c>
       <c r="AD5" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1703,7 +1703,7 @@
         <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1712,7 +1712,7 @@
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,49 +1721,49 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS5" t="n">
         <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW5" t="n">
         <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>9.199999999999999</v>
@@ -1772,10 +1772,10 @@
         <v>9.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
         <v>7.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nigerian Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Barau FC</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J2" t="n">
+        <v>110</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>330</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="n">
         <v>6.2</v>
       </c>
-      <c r="H2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.43</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nigerian Premier League</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="S3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA3" t="n">
         <v>210</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>65</v>
       </c>
       <c r="AC3" t="n">
-        <v>850</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>850</v>
+        <v>70</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,515 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Swedish Superettan</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>14:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Helsingborgs</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Landskrona</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-11 13:45:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Icelandic 3 Deild</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ymir</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>KA Asvellir</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>970</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,34 +881,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>6.4</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>330</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,103 +920,103 @@
         <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.28</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK2" t="n">
         <v>14</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,261 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Icelandic 3 Deild</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ymir</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>KA Asvellir</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>970</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Icelandic 3 Deild</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ymir</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>KA Asvellir</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
